--- a/output/pdf_financials_xlsx/DML.xlsx
+++ b/output/pdf_financials_xlsx/DML.xlsx
@@ -5795,7 +5795,7 @@
         <v>-4.709</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>104.862</v>
+        <v>32.964</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>3.584</v>

--- a/output/pdf_financials_xlsx/DML.xlsx
+++ b/output/pdf_financials_xlsx/DML.xlsx
@@ -6995,19 +6995,19 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="113">
@@ -40385,7 +40385,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DML.xlsx
+++ b/output/pdf_financials_xlsx/DML.xlsx
@@ -1306,10 +1306,10 @@
         <v>87.021</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-90.648</v>
+        <v>-90.883</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-217.288</v>
+        <v>-210.656</v>
       </c>
     </row>
     <row r="17">
@@ -1364,10 +1364,10 @@
         <v>-1.011</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0.471</v>
+        <v>-0.236</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>-6.632</v>
       </c>
     </row>
     <row r="18">
@@ -1579,16 +1579,16 @@
         <v>-83.83499999999999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-31.703</v>
+        <v>-28.266</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-51.56</v>
+        <v>-16.717</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-17.343</v>
+        <v>-11.699</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-19.563</v>
+        <v>-19.454</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-30.077</v>
@@ -1606,7 +1606,7 @@
         <v>89.364</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-91.119</v>
+        <v>-91.59</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>-217.288</v>
@@ -1640,13 +1640,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-34.843</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-5.644</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-0.109</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -2040,10 +2040,10 @@
         <v>87.021</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-90.648</v>
+        <v>-90.883</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-217.288</v>
+        <v>-210.656</v>
       </c>
     </row>
     <row r="28">
@@ -2156,10 +2156,10 @@
         <v>87.021</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-90.648</v>
+        <v>-90.883</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-217.288</v>
+        <v>-210.656</v>
       </c>
     </row>
     <row r="30">
@@ -2214,10 +2214,10 @@
         <v>4691.159029649596</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-2253.24384787472</v>
+        <v>-2259.0852597564</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-4418.218788125254</v>
+        <v>-4283.36722244815</v>
       </c>
     </row>
     <row r="31">
@@ -2272,10 +2272,10 @@
         <v>1.161788533802186</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.5195922689965581</v>
+        <v>-0.2596745265891311</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.148260671426401</v>
       </c>
     </row>
     <row r="32">
@@ -3660,34 +3660,34 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>745.0839999999999</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>393.412</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>390.095</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>374.849</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>248.119</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>281.226</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>270.586</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>188.415</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>188.153</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>252.575</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>0</v>
@@ -3718,34 +3718,34 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>27.651</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>48.598</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>68.7</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>7.479</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="L57" s="3" t="n">
         <v>0</v>
@@ -7133,13 +7133,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.316</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>11.128</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>8.118</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -39692,7 +39692,11 @@
           <t>Deferred income tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -42967,7 +42971,11 @@
           <t>Deferred income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -45650,7 +45658,11 @@
           <t>Deferred income tax recovery (note 16)</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -47438,7 +47450,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -51012,7 +51028,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -53811,7 +53831,11 @@
           <t>Deferred income tax recovery (note 18)</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -57383,7 +57407,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -59317,7 +59345,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -60889,7 +60921,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -63451,7 +63487,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -64251,7 +64291,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -64449,7 +64493,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E568" s="5" t="n">
         <v>1.316</v>
       </c>
@@ -67284,7 +67332,11 @@
           <t>Deferred Income tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -67383,7 +67435,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E598" t="inlineStr">
         <is>
           <t>-</t>
@@ -73610,7 +73666,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr">
         <is>
           <t>-</t>
@@ -73709,7 +73769,11 @@
           <t>Net loss from discontinued operations (note 6)</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E662" t="inlineStr">
         <is>
           <t>-</t>
@@ -74673,7 +74737,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E672" t="inlineStr">
         <is>
           <t>-</t>
@@ -74768,7 +74836,11 @@
           <t>Net loss from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
           <t>-</t>
